--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-procedure.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-procedure.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-11T08:25:56+00:00</t>
+    <t>2026-09-14T07:00:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-procedure.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-procedure.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-14T07:00:54+00:00</t>
+    <t>2026-09-14T09:05:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-procedure.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-procedure.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2186" uniqueCount="453">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2187" uniqueCount="455">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-14T09:05:35+00:00</t>
+    <t>2026-09-14T11:50:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -625,7 +625,7 @@
     <t>Procedure.status</t>
   </si>
   <si>
-    <t>Nur tatsächlich durchgeführte (completed) oder irrtümlich dokumentierte (entered-in-error) Prozeduren.</t>
+    <t>Nur tatsächlich durchgeführte (completed) Prozeduren werden in der e-Diagnose dokumentiert.</t>
   </si>
   <si>
     <t>A code specifying the state of the procedure. Generally, this will be the in-progress or completed state.</t>
@@ -635,10 +635,16 @@
 This element is labeled as a modifier because the status contains codes that mark the resource as not currently valid.</t>
   </si>
   <si>
+    <t>completed</t>
+  </si>
+  <si>
     <t>required</t>
   </si>
   <si>
-    <t>https://fhir.hl7.at/elga/ediag/r4/ValueSet/at-ediag-procedure-status</t>
+    <t>A code specifying the state of the procedure.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/event-status|4.0.1</t>
   </si>
   <si>
     <t>Event.status</t>
@@ -661,7 +667,7 @@
 </t>
   </si>
   <si>
-    <t>ToDo: Korrekturvermerk wird von digimed übernommen, ist noch in Abstimmung.</t>
+    <t>Begründung für den Status der Prozedur nicht relevant.</t>
   </si>
   <si>
     <t>Captures the reason for the current state of the procedure.</t>
@@ -722,7 +728,7 @@
     <t>0..1 to account for primarily narrative only resources.</t>
   </si>
   <si>
-    <t>https://fhir.hl7.at/elga/ediag/r4/ValueSet/at-ediag-prozeduren-codes</t>
+    <t>https://fhir.hl7.at/elga/ediag/r4/ValueSet/at-ediag-procedure-code</t>
   </si>
   <si>
     <t>Event.code</t>
@@ -1780,7 +1786,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="62.6328125" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="54.46484375" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="52.95703125" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
@@ -3779,7 +3785,7 @@
       </c>
       <c r="Q18" s="2"/>
       <c r="R18" t="s" s="2">
-        <v>21</v>
+        <v>197</v>
       </c>
       <c r="S18" t="s" s="2">
         <v>21</v>
@@ -3797,11 +3803,13 @@
         <v>21</v>
       </c>
       <c r="X18" t="s" s="2">
-        <v>197</v>
-      </c>
-      <c r="Y18" s="2"/>
+        <v>198</v>
+      </c>
+      <c r="Y18" t="s" s="2">
+        <v>199</v>
+      </c>
       <c r="Z18" t="s" s="2">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="AA18" t="s" s="2">
         <v>21</v>
@@ -3834,13 +3842,13 @@
         <v>99</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="AN18" t="s" s="2">
         <v>21</v>
@@ -3848,21 +3856,21 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G19" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="H19" t="s" s="2">
         <v>21</v>
@@ -3874,16 +3882,16 @@
         <v>88</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
@@ -3909,13 +3917,13 @@
         <v>21</v>
       </c>
       <c r="X19" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="Y19" t="s" s="2">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="Z19" t="s" s="2">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="AA19" t="s" s="2">
         <v>21</v>
@@ -3933,7 +3941,7 @@
         <v>21</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>78</v>
@@ -3948,10 +3956,10 @@
         <v>99</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="AM19" t="s" s="2">
         <v>21</v>
@@ -3962,10 +3970,10 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -3988,13 +3996,13 @@
         <v>88</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -4021,13 +4029,13 @@
         <v>21</v>
       </c>
       <c r="X20" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="Y20" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="Z20" t="s" s="2">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="AA20" t="s" s="2">
         <v>21</v>
@@ -4045,7 +4053,7 @@
         <v>21</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>78</v>
@@ -4063,10 +4071,10 @@
         <v>21</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="AN20" t="s" s="2">
         <v>21</v>
@@ -4074,14 +4082,14 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
@@ -4100,17 +4108,17 @@
         <v>88</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" t="s" s="2">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="P21" t="s" s="2">
         <v>21</v>
@@ -4135,11 +4143,11 @@
         <v>21</v>
       </c>
       <c r="X21" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Y21" s="2"/>
       <c r="Z21" t="s" s="2">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="AA21" t="s" s="2">
         <v>21</v>
@@ -4157,7 +4165,7 @@
         <v>21</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>78</v>
@@ -4172,24 +4180,24 @@
         <v>99</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>229</v>
+        <v>231</v>
       </c>
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4212,13 +4220,13 @@
         <v>21</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
@@ -4269,7 +4277,7 @@
         <v>21</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>78</v>
@@ -4287,7 +4295,7 @@
         <v>21</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="AM22" t="s" s="2">
         <v>21</v>
@@ -4298,10 +4306,10 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4327,10 +4335,10 @@
         <v>132</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="N23" t="s" s="2">
         <v>154</v>
@@ -4374,7 +4382,7 @@
         <v>135</v>
       </c>
       <c r="AC23" t="s" s="2">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="AD23" t="s" s="2">
         <v>21</v>
@@ -4383,7 +4391,7 @@
         <v>136</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>78</v>
@@ -4401,7 +4409,7 @@
         <v>21</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="AM23" t="s" s="2">
         <v>21</v>
@@ -4412,10 +4420,10 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4438,19 +4446,19 @@
         <v>88</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="O24" t="s" s="2">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>21</v>
@@ -4499,7 +4507,7 @@
         <v>21</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>78</v>
@@ -4517,21 +4525,21 @@
         <v>21</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="AM24" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4554,19 +4562,19 @@
         <v>88</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="O25" t="s" s="2">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>21</v>
@@ -4615,7 +4623,7 @@
         <v>21</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>78</v>
@@ -4633,25 +4641,25 @@
         <v>21</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="AM25" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>257</v>
+        <v>259</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
@@ -4670,13 +4678,13 @@
         <v>88</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
@@ -4727,7 +4735,7 @@
         <v>21</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>87</v>
@@ -4742,24 +4750,24 @@
         <v>99</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>266</v>
+        <v>268</v>
       </c>
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4782,16 +4790,16 @@
         <v>88</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
@@ -4841,7 +4849,7 @@
         <v>21</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>78</v>
@@ -4856,24 +4864,24 @@
         <v>99</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>275</v>
+        <v>277</v>
       </c>
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4896,16 +4904,16 @@
         <v>88</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
@@ -4955,7 +4963,7 @@
         <v>21</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>78</v>
@@ -4970,24 +4978,24 @@
         <v>99</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>284</v>
+        <v>286</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5010,13 +5018,13 @@
         <v>88</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
@@ -5067,7 +5075,7 @@
         <v>21</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>78</v>
@@ -5085,10 +5093,10 @@
         <v>21</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="AN29" t="s" s="2">
         <v>21</v>
@@ -5096,10 +5104,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5122,13 +5130,13 @@
         <v>88</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -5179,7 +5187,7 @@
         <v>21</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>78</v>
@@ -5197,10 +5205,10 @@
         <v>21</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="AN30" t="s" s="2">
         <v>21</v>
@@ -5208,10 +5216,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5234,13 +5242,13 @@
         <v>88</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -5291,7 +5299,7 @@
         <v>21</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>78</v>
@@ -5306,10 +5314,10 @@
         <v>99</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="AM31" t="s" s="2">
         <v>21</v>
@@ -5320,10 +5328,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5346,13 +5354,13 @@
         <v>21</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -5403,7 +5411,7 @@
         <v>21</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>78</v>
@@ -5421,7 +5429,7 @@
         <v>21</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="AM32" t="s" s="2">
         <v>21</v>
@@ -5432,10 +5440,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5461,10 +5469,10 @@
         <v>132</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="N33" t="s" s="2">
         <v>154</v>
@@ -5517,7 +5525,7 @@
         <v>21</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>78</v>
@@ -5535,7 +5543,7 @@
         <v>21</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="AM33" t="s" s="2">
         <v>21</v>
@@ -5546,14 +5554,14 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
@@ -5575,10 +5583,10 @@
         <v>132</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="N34" t="s" s="2">
         <v>154</v>
@@ -5633,7 +5641,7 @@
         <v>21</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>78</v>
@@ -5662,10 +5670,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5688,17 +5696,17 @@
         <v>88</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" t="s" s="2">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>21</v>
@@ -5723,13 +5731,13 @@
         <v>21</v>
       </c>
       <c r="X35" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="Y35" t="s" s="2">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="Z35" t="s" s="2">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="AA35" t="s" s="2">
         <v>21</v>
@@ -5747,7 +5755,7 @@
         <v>21</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>78</v>
@@ -5762,24 +5770,24 @@
         <v>99</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="AM35" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>318</v>
+        <v>320</v>
       </c>
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5802,17 +5810,17 @@
         <v>88</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" t="s" s="2">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>21</v>
@@ -5861,7 +5869,7 @@
         <v>21</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>87</v>
@@ -5876,24 +5884,24 @@
         <v>99</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>327</v>
+        <v>329</v>
       </c>
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5916,17 +5924,17 @@
         <v>21</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" t="s" s="2">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>21</v>
@@ -5975,7 +5983,7 @@
         <v>21</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>78</v>
@@ -5993,7 +6001,7 @@
         <v>21</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="AM37" t="s" s="2">
         <v>21</v>
@@ -6004,10 +6012,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6030,17 +6038,17 @@
         <v>88</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" t="s" s="2">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>21</v>
@@ -6089,7 +6097,7 @@
         <v>21</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>78</v>
@@ -6107,10 +6115,10 @@
         <v>21</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="AN38" t="s" s="2">
         <v>21</v>
@@ -6118,10 +6126,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6144,16 +6152,16 @@
         <v>88</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
@@ -6179,13 +6187,13 @@
         <v>21</v>
       </c>
       <c r="X39" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="Y39" t="s" s="2">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="Z39" t="s" s="2">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="AA39" t="s" s="2">
         <v>21</v>
@@ -6203,7 +6211,7 @@
         <v>21</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>78</v>
@@ -6218,13 +6226,13 @@
         <v>99</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="AN39" t="s" s="2">
         <v>21</v>
@@ -6232,10 +6240,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6258,16 +6266,16 @@
         <v>88</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
@@ -6317,7 +6325,7 @@
         <v>21</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>78</v>
@@ -6332,13 +6340,13 @@
         <v>99</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="AN40" t="s" s="2">
         <v>21</v>
@@ -6346,10 +6354,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6372,16 +6380,16 @@
         <v>88</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
@@ -6407,13 +6415,13 @@
         <v>21</v>
       </c>
       <c r="X41" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="Y41" t="s" s="2">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="Z41" t="s" s="2">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="AA41" t="s" s="2">
         <v>21</v>
@@ -6431,7 +6439,7 @@
         <v>21</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>78</v>
@@ -6449,21 +6457,21 @@
         <v>21</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="AM41" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>363</v>
+        <v>365</v>
       </c>
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6486,16 +6494,16 @@
         <v>88</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -6521,13 +6529,13 @@
         <v>21</v>
       </c>
       <c r="X42" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="Y42" t="s" s="2">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="Z42" t="s" s="2">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="AA42" t="s" s="2">
         <v>21</v>
@@ -6545,7 +6553,7 @@
         <v>21</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>78</v>
@@ -6563,7 +6571,7 @@
         <v>21</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="AM42" t="s" s="2">
         <v>21</v>
@@ -6574,10 +6582,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6600,16 +6608,16 @@
         <v>21</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
@@ -6659,7 +6667,7 @@
         <v>21</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>78</v>
@@ -6677,7 +6685,7 @@
         <v>21</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="AM43" t="s" s="2">
         <v>21</v>
@@ -6688,10 +6696,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6714,16 +6722,16 @@
         <v>21</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
@@ -6749,13 +6757,13 @@
         <v>21</v>
       </c>
       <c r="X44" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="Y44" t="s" s="2">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="Z44" t="s" s="2">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="AA44" t="s" s="2">
         <v>21</v>
@@ -6773,7 +6781,7 @@
         <v>21</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>78</v>
@@ -6791,7 +6799,7 @@
         <v>21</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="AM44" t="s" s="2">
         <v>21</v>
@@ -6802,10 +6810,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6828,17 +6836,17 @@
         <v>21</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" t="s" s="2">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>21</v>
@@ -6887,7 +6895,7 @@
         <v>21</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>78</v>
@@ -6905,7 +6913,7 @@
         <v>21</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="AM45" t="s" s="2">
         <v>21</v>
@@ -6916,10 +6924,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -6942,13 +6950,13 @@
         <v>21</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -6975,13 +6983,13 @@
         <v>21</v>
       </c>
       <c r="X46" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="Y46" t="s" s="2">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="Z46" t="s" s="2">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="AA46" t="s" s="2">
         <v>21</v>
@@ -6999,7 +7007,7 @@
         <v>21</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>78</v>
@@ -7017,7 +7025,7 @@
         <v>21</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="AM46" t="s" s="2">
         <v>21</v>
@@ -7028,10 +7036,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7054,13 +7062,13 @@
         <v>21</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
@@ -7111,7 +7119,7 @@
         <v>21</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>78</v>
@@ -7126,24 +7134,24 @@
         <v>99</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="AM47" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>401</v>
+        <v>403</v>
       </c>
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7166,13 +7174,13 @@
         <v>21</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" s="2"/>
@@ -7223,7 +7231,7 @@
         <v>21</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>78</v>
@@ -7241,7 +7249,7 @@
         <v>21</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="AM48" t="s" s="2">
         <v>21</v>
@@ -7252,10 +7260,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7281,10 +7289,10 @@
         <v>132</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="N49" t="s" s="2">
         <v>154</v>
@@ -7328,7 +7336,7 @@
         <v>135</v>
       </c>
       <c r="AC49" t="s" s="2">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="AD49" t="s" s="2">
         <v>21</v>
@@ -7337,7 +7345,7 @@
         <v>136</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>78</v>
@@ -7355,7 +7363,7 @@
         <v>21</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="AM49" t="s" s="2">
         <v>21</v>
@@ -7366,10 +7374,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7392,16 +7400,16 @@
         <v>88</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
@@ -7451,7 +7459,7 @@
         <v>21</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>78</v>
@@ -7469,7 +7477,7 @@
         <v>21</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="AM50" t="s" s="2">
         <v>21</v>
@@ -7480,10 +7488,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7506,13 +7514,13 @@
         <v>88</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -7563,7 +7571,7 @@
         <v>21</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>78</v>
@@ -7581,7 +7589,7 @@
         <v>21</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="AM51" t="s" s="2">
         <v>21</v>
@@ -7592,10 +7600,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7618,13 +7626,13 @@
         <v>88</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
@@ -7675,7 +7683,7 @@
         <v>21</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>87</v>
@@ -7693,7 +7701,7 @@
         <v>21</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="AM52" t="s" s="2">
         <v>21</v>
@@ -7704,10 +7712,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7730,13 +7738,13 @@
         <v>21</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -7787,7 +7795,7 @@
         <v>21</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>78</v>
@@ -7805,7 +7813,7 @@
         <v>21</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="AM53" t="s" s="2">
         <v>21</v>
@@ -7816,10 +7824,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -7842,13 +7850,13 @@
         <v>21</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" s="2"/>
@@ -7899,7 +7907,7 @@
         <v>21</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>78</v>
@@ -7917,7 +7925,7 @@
         <v>21</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="AM54" t="s" s="2">
         <v>21</v>
@@ -7928,10 +7936,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -7957,10 +7965,10 @@
         <v>132</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="N55" t="s" s="2">
         <v>154</v>
@@ -8013,7 +8021,7 @@
         <v>21</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>78</v>
@@ -8031,7 +8039,7 @@
         <v>21</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="AM55" t="s" s="2">
         <v>21</v>
@@ -8042,14 +8050,14 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
@@ -8071,10 +8079,10 @@
         <v>132</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="N56" t="s" s="2">
         <v>154</v>
@@ -8129,7 +8137,7 @@
         <v>21</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>78</v>
@@ -8158,10 +8166,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8184,13 +8192,13 @@
         <v>21</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
@@ -8220,10 +8228,10 @@
         <v>111</v>
       </c>
       <c r="Y57" t="s" s="2">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="Z57" t="s" s="2">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="AA57" t="s" s="2">
         <v>21</v>
@@ -8241,7 +8249,7 @@
         <v>21</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>78</v>
@@ -8259,7 +8267,7 @@
         <v>21</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="AM57" t="s" s="2">
         <v>21</v>
@@ -8270,10 +8278,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8296,13 +8304,13 @@
         <v>21</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" s="2"/>
@@ -8353,7 +8361,7 @@
         <v>21</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>87</v>
@@ -8371,7 +8379,7 @@
         <v>21</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="AM58" t="s" s="2">
         <v>21</v>
@@ -8382,10 +8390,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8408,19 +8416,19 @@
         <v>21</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="O59" t="s" s="2">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>21</v>
@@ -8469,7 +8477,7 @@
         <v>21</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>78</v>
@@ -8487,7 +8495,7 @@
         <v>21</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="AM59" t="s" s="2">
         <v>21</v>
@@ -8498,10 +8506,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8524,16 +8532,16 @@
         <v>21</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
@@ -8559,13 +8567,13 @@
         <v>21</v>
       </c>
       <c r="X60" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="Y60" t="s" s="2">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="Z60" t="s" s="2">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="AA60" t="s" s="2">
         <v>21</v>
@@ -8583,7 +8591,7 @@
         <v>21</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>78</v>
@@ -8601,7 +8609,7 @@
         <v>21</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="AM60" t="s" s="2">
         <v>21</v>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-procedure.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-procedure.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-14T11:50:31+00:00</t>
+    <t>2026-09-15T06:30:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-procedure.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-procedure.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-15T06:30:22+00:00</t>
+    <t>2026-09-15T08:16:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-procedure.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-procedure.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-15T08:16:05+00:00</t>
+    <t>2026-09-16T05:34:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -719,7 +719,7 @@
 </t>
   </si>
   <si>
-    <t>Prozedurencode der durchgeführten Prozedur.</t>
+    <t>Prozedurencode der durchgeführten Prozedur; Freitext ist nicht zulässig.</t>
   </si>
   <si>
     <t>The specific procedure that is performed. Use text if the exact nature of the procedure cannot be coded (e.g. "Laparoscopic Appendectomy").</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-procedure.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-procedure.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-16T05:34:40+00:00</t>
+    <t>2026-09-17T07:46:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-procedure.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-procedure.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-17T07:46:21+00:00</t>
+    <t>2026-09-17T12:50:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-procedure.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-procedure.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-17T12:50:52+00:00</t>
+    <t>2026-09-18T07:26:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-procedure.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-procedure.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-18T07:26:42+00:00</t>
+    <t>2026-09-29T15:00:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-procedure.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-procedure.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AN$60</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AN$69</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2187" uniqueCount="455">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2513" uniqueCount="521">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-29T15:00:21+00:00</t>
+    <t>2026-09-30T11:14:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -515,7 +515,7 @@
 </t>
   </si>
   <si>
-    <t>Zuordnung der Diagnose in einem internen Dokumentationssystem.</t>
+    <t>External Identifiers for this procedure</t>
   </si>
   <si>
     <t>Business identifiers assigned to this procedure by the performer or other systems which remain constant as the resource is updated and is propagated from server to server.</t>
@@ -527,6 +527,10 @@
     <t>Allows identification of the procedure as it is known by various participating systems and in a way that remains consistent across servers.</t>
   </si>
   <si>
+    <t xml:space="preserve">value:system}
+</t>
+  </si>
+  <si>
     <t>Event.identifier</t>
   </si>
   <si>
@@ -537,6 +541,241 @@
   </si>
   <si>
     <t>Some combination of ORC-2 / ORC-3 / OBR-2 / OBR-3 / IPC-1 / IPC-2 / IPC-3 / IPC-4</t>
+  </si>
+  <si>
+    <t>Procedure.identifier:businessIdentifier</t>
+  </si>
+  <si>
+    <t>businessIdentifier</t>
+  </si>
+  <si>
+    <t>Identifier innerhalb der e-Diagnose für einen Eintrag.</t>
+  </si>
+  <si>
+    <t>Dieser Identifier wird von der Fachanwendung e-Diagnose vergeben, sollte dieser durch den Client nicht gesetzt werden. Ein Client kann diesen Identifier nutzen, um einzelne Einträge im Zuge einer Bearbeitung miteinander zu verknüpfen.</t>
+  </si>
+  <si>
+    <t>Procedure.identifier:businessIdentifier.id</t>
+  </si>
+  <si>
+    <t>Procedure.identifier.id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">string
+</t>
+  </si>
+  <si>
+    <t>Unique id for inter-element referencing</t>
+  </si>
+  <si>
+    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
+  </si>
+  <si>
+    <t>Element.id</t>
+  </si>
+  <si>
+    <t>n/a</t>
+  </si>
+  <si>
+    <t>Procedure.identifier:businessIdentifier.extension</t>
+  </si>
+  <si>
+    <t>Procedure.identifier.extension</t>
+  </si>
+  <si>
+    <t>Additional content defined by implementations</t>
+  </si>
+  <si>
+    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
+  </si>
+  <si>
+    <t>Extensions are always sliced by (at least) url</t>
+  </si>
+  <si>
+    <t>Element.extension</t>
+  </si>
+  <si>
+    <t>Procedure.identifier:businessIdentifier.use</t>
+  </si>
+  <si>
+    <t>Procedure.identifier.use</t>
+  </si>
+  <si>
+    <t>usual | official | temp | secondary | old (If known)</t>
+  </si>
+  <si>
+    <t>The purpose of this identifier.</t>
+  </si>
+  <si>
+    <t>Applications can assume that an identifier is permanent unless it explicitly says that it is temporary.</t>
+  </si>
+  <si>
+    <t>Allows the appropriate identifier for a particular context of use to be selected from among a set of identifiers.</t>
+  </si>
+  <si>
+    <t>required</t>
+  </si>
+  <si>
+    <t>Identifies the purpose for this identifier, if known .</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/identifier-use|4.0.1</t>
+  </si>
+  <si>
+    <t>Identifier.use</t>
+  </si>
+  <si>
+    <t>Role.code or implied by context</t>
+  </si>
+  <si>
+    <t>Procedure.identifier:businessIdentifier.type</t>
+  </si>
+  <si>
+    <t>Procedure.identifier.type</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CodeableConcept
+</t>
+  </si>
+  <si>
+    <t>Description of identifier</t>
+  </si>
+  <si>
+    <t>A coded type for the identifier that can be used to determine which identifier to use for a specific purpose.</t>
+  </si>
+  <si>
+    <t>This element deals only with general categories of identifiers.  It SHOULD not be used for codes that correspond 1..1 with the Identifier.system. Some identifiers may fall into multiple categories due to common usage.   Where the system is known, a type is unnecessary because the type is always part of the system definition. However systems often need to handle identifiers where the system is not known. There is not a 1:1 relationship between type and system, since many different systems have the same type.</t>
+  </si>
+  <si>
+    <t>Allows users to make use of identifiers when the identifier system is not known.</t>
+  </si>
+  <si>
+    <t>extensible</t>
+  </si>
+  <si>
+    <t>A coded type for an identifier that can be used to determine which identifier to use for a specific purpose.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/identifier-type|4.0.1</t>
+  </si>
+  <si>
+    <t>Identifier.type</t>
+  </si>
+  <si>
+    <t>CX.5</t>
+  </si>
+  <si>
+    <t>Procedure.identifier:businessIdentifier.system</t>
+  </si>
+  <si>
+    <t>Procedure.identifier.system</t>
+  </si>
+  <si>
+    <t>The namespace for the identifier value</t>
+  </si>
+  <si>
+    <t>Establishes the namespace for the value - that is, a URL that describes a set values that are unique.</t>
+  </si>
+  <si>
+    <t>Identifier.system is always case sensitive.</t>
+  </si>
+  <si>
+    <t>There are many sets  of identifiers.  To perform matching of two identifiers, we need to know what set we're dealing with. The system identifies a particular set of unique identifiers.</t>
+  </si>
+  <si>
+    <t>https://fhir.hl7.at/elga/ediag/r4/CodeSystem/at-ediag-codesystem-business-identifier</t>
+  </si>
+  <si>
+    <t>http://www.acme.com/identifiers/patient</t>
+  </si>
+  <si>
+    <t>Identifier.system</t>
+  </si>
+  <si>
+    <t>II.root or Role.id.root</t>
+  </si>
+  <si>
+    <t>CX.4 / EI-2-4</t>
+  </si>
+  <si>
+    <t>Procedure.identifier:businessIdentifier.value</t>
+  </si>
+  <si>
+    <t>Procedure.identifier.value</t>
+  </si>
+  <si>
+    <t>The value that is unique</t>
+  </si>
+  <si>
+    <t>The portion of the identifier typically relevant to the user and which is unique within the context of the system.</t>
+  </si>
+  <si>
+    <t>If the value is a full URI, then the system SHALL be urn:ietf:rfc:3986.  The value's primary purpose is computational mapping.  As a result, it may be normalized for comparison purposes (e.g. removing non-significant whitespace, dashes, etc.)  A value formatted for human display can be conveyed using the [Rendered Value extension](http://hl7.org/fhir/R4/extension-rendered-value.html). Identifier.value is to be treated as case sensitive unless knowledge of the Identifier.system allows the processer to be confident that non-case-sensitive processing is safe.</t>
+  </si>
+  <si>
+    <t>123456</t>
+  </si>
+  <si>
+    <t>Identifier.value</t>
+  </si>
+  <si>
+    <t>II.extension or II.root if system indicates OID or GUID (Or Role.id.extension or root)</t>
+  </si>
+  <si>
+    <t>CX.1 / EI.1</t>
+  </si>
+  <si>
+    <t>Procedure.identifier:businessIdentifier.period</t>
+  </si>
+  <si>
+    <t>Procedure.identifier.period</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Period
+</t>
+  </si>
+  <si>
+    <t>Time period when id is/was valid for use</t>
+  </si>
+  <si>
+    <t>Time period during which identifier is/was valid for use.</t>
+  </si>
+  <si>
+    <t>Identifier.period</t>
+  </si>
+  <si>
+    <t>Role.effectiveTime or implied by context</t>
+  </si>
+  <si>
+    <t>CX.7 + CX.8</t>
+  </si>
+  <si>
+    <t>Procedure.identifier:businessIdentifier.assigner</t>
+  </si>
+  <si>
+    <t>Procedure.identifier.assigner</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(Organization|4.0.1)
+</t>
+  </si>
+  <si>
+    <t>Organization that issued id (may be just text)</t>
+  </si>
+  <si>
+    <t>Organization that issued/manages the identifier.</t>
+  </si>
+  <si>
+    <t>The Identifier.assigner may omit the .reference element and only contain a .display element reflecting the name or other textual information about the assigning organization.</t>
+  </si>
+  <si>
+    <t>Identifier.assigner</t>
+  </si>
+  <si>
+    <t>II.assigningAuthorityName but note that this is an improper use by the definition of the field.  Also Role.scoper</t>
+  </si>
+  <si>
+    <t>CX.4 / (CX.4,CX.9,CX.10)</t>
   </si>
   <si>
     <t>Procedure.instantiatesCanonical</t>
@@ -638,9 +877,6 @@
     <t>completed</t>
   </si>
   <si>
-    <t>required</t>
-  </si>
-  <si>
     <t>A code specifying the state of the procedure.</t>
   </si>
   <si>
@@ -663,10 +899,6 @@
 Cancelled Reason</t>
   </si>
   <si>
-    <t xml:space="preserve">CodeableConcept
-</t>
-  </si>
-  <si>
     <t>Begründung für den Status der Prozedur nicht relevant.</t>
   </si>
   <si>
@@ -746,35 +978,7 @@
     <t>Procedure.code.id</t>
   </si>
   <si>
-    <t xml:space="preserve">string
-</t>
-  </si>
-  <si>
-    <t>Unique id for inter-element referencing</t>
-  </si>
-  <si>
-    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
-  </si>
-  <si>
-    <t>Element.id</t>
-  </si>
-  <si>
-    <t>n/a</t>
-  </si>
-  <si>
     <t>Procedure.code.extension</t>
-  </si>
-  <si>
-    <t>Additional content defined by implementations</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
-  </si>
-  <si>
-    <t>Extensions are always sliced by (at least) url</t>
-  </si>
-  <si>
-    <t>Element.extension</t>
   </si>
   <si>
     <t>Procedure.code.coding</t>
@@ -1050,10 +1254,6 @@
   </si>
   <si>
     <t>Procedure.performer.onBehalfOf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(Organization|4.0.1)
-</t>
   </si>
   <si>
     <t>Organization the device or practitioner was acting for</t>
@@ -1758,12 +1958,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AN60"/>
+  <dimension ref="A1:AN69"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="33.2890625" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="39.09375" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="33.2890625" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="13.48828125" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="3" max="3" width="14.828125" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
@@ -1780,12 +1980,12 @@
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="8.53515625" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="32.7734375" customWidth="true" bestFit="true"/>
     <col min="21" max="21" width="14.72265625" customWidth="true" bestFit="true"/>
     <col min="22" max="22" width="15.13671875" customWidth="true" bestFit="true"/>
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="62.6328125" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="84.33984375" customWidth="true" bestFit="true"/>
     <col min="26" max="26" width="52.95703125" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
@@ -3249,16 +3449,14 @@
         <v>21</v>
       </c>
       <c r="AB13" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC13" t="s" s="2">
-        <v>21</v>
-      </c>
+        <v>163</v>
+      </c>
+      <c r="AC13" s="2"/>
       <c r="AD13" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE13" t="s" s="2">
-        <v>21</v>
+        <v>136</v>
       </c>
       <c r="AF13" t="s" s="2">
         <v>157</v>
@@ -3276,26 +3474,28 @@
         <v>99</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="AL13" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="AM13" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="AN13" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>167</v>
-      </c>
-      <c r="C14" s="2"/>
+        <v>157</v>
+      </c>
+      <c r="C14" t="s" s="2">
+        <v>169</v>
+      </c>
       <c r="D14" t="s" s="2">
         <v>21</v>
       </c>
@@ -3304,7 +3504,7 @@
         <v>78</v>
       </c>
       <c r="G14" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="H14" t="s" s="2">
         <v>21</v>
@@ -3316,16 +3516,20 @@
         <v>88</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>168</v>
+        <v>158</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>170</v>
-      </c>
-      <c r="N14" s="2"/>
-      <c r="O14" s="2"/>
+        <v>171</v>
+      </c>
+      <c r="N14" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="O14" t="s" s="2">
+        <v>162</v>
+      </c>
       <c r="P14" t="s" s="2">
         <v>21</v>
       </c>
@@ -3373,7 +3577,7 @@
         <v>21</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>167</v>
+        <v>157</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>78</v>
@@ -3388,21 +3592,21 @@
         <v>99</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>171</v>
+        <v>164</v>
       </c>
       <c r="AL14" t="s" s="2">
-        <v>172</v>
+        <v>165</v>
       </c>
       <c r="AM14" t="s" s="2">
-        <v>21</v>
+        <v>166</v>
       </c>
       <c r="AN14" t="s" s="2">
-        <v>21</v>
+        <v>167</v>
       </c>
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B15" t="s" s="2">
         <v>173</v>
@@ -3416,7 +3620,7 @@
         <v>78</v>
       </c>
       <c r="G15" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="H15" t="s" s="2">
         <v>21</v>
@@ -3425,20 +3629,18 @@
         <v>21</v>
       </c>
       <c r="J15" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>101</v>
+        <v>174</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>175</v>
-      </c>
-      <c r="N15" t="s" s="2">
         <v>176</v>
       </c>
+      <c r="N15" s="2"/>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
         <v>21</v>
@@ -3487,25 +3689,25 @@
         <v>21</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH15" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI15" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ15" t="s" s="2">
-        <v>99</v>
+        <v>21</v>
       </c>
       <c r="AK15" t="s" s="2">
-        <v>177</v>
+        <v>21</v>
       </c>
       <c r="AL15" t="s" s="2">
-        <v>172</v>
+        <v>178</v>
       </c>
       <c r="AM15" t="s" s="2">
         <v>21</v>
@@ -3516,21 +3718,21 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>179</v>
+        <v>151</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G16" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H16" t="s" s="2">
         <v>21</v>
@@ -3539,10 +3741,10 @@
         <v>21</v>
       </c>
       <c r="J16" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>180</v>
+        <v>132</v>
       </c>
       <c r="L16" t="s" s="2">
         <v>181</v>
@@ -3550,7 +3752,9 @@
       <c r="M16" t="s" s="2">
         <v>182</v>
       </c>
-      <c r="N16" s="2"/>
+      <c r="N16" t="s" s="2">
+        <v>154</v>
+      </c>
       <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
         <v>21</v>
@@ -3587,19 +3791,19 @@
         <v>21</v>
       </c>
       <c r="AB16" t="s" s="2">
-        <v>21</v>
+        <v>135</v>
       </c>
       <c r="AC16" t="s" s="2">
-        <v>21</v>
+        <v>183</v>
       </c>
       <c r="AD16" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE16" t="s" s="2">
-        <v>21</v>
+        <v>136</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>178</v>
+        <v>184</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>78</v>
@@ -3611,13 +3815,13 @@
         <v>21</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>183</v>
+        <v>21</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>184</v>
+        <v>178</v>
       </c>
       <c r="AM16" t="s" s="2">
         <v>21</v>
@@ -3631,41 +3835,43 @@
         <v>185</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>186</v>
+        <v>21</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G17" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="H17" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I17" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="J17" t="s" s="2">
         <v>88</v>
       </c>
       <c r="K17" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="L17" t="s" s="2">
         <v>187</v>
       </c>
-      <c r="L17" t="s" s="2">
+      <c r="M17" t="s" s="2">
         <v>188</v>
       </c>
-      <c r="M17" t="s" s="2">
+      <c r="N17" t="s" s="2">
         <v>189</v>
       </c>
-      <c r="N17" t="s" s="2">
+      <c r="O17" t="s" s="2">
         <v>190</v>
       </c>
-      <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
         <v>21</v>
       </c>
@@ -3689,13 +3895,13 @@
         <v>21</v>
       </c>
       <c r="X17" t="s" s="2">
-        <v>21</v>
+        <v>191</v>
       </c>
       <c r="Y17" t="s" s="2">
-        <v>21</v>
+        <v>192</v>
       </c>
       <c r="Z17" t="s" s="2">
-        <v>21</v>
+        <v>193</v>
       </c>
       <c r="AA17" t="s" s="2">
         <v>21</v>
@@ -3713,13 +3919,13 @@
         <v>21</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>185</v>
+        <v>194</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH17" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI17" t="s" s="2">
         <v>21</v>
@@ -3728,24 +3934,24 @@
         <v>99</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>191</v>
+        <v>21</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="AM17" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN17" t="s" s="2">
-        <v>21</v>
+        <v>130</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3753,39 +3959,41 @@
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="G18" t="s" s="2">
         <v>87</v>
       </c>
       <c r="H18" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="I18" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="J18" t="s" s="2">
         <v>88</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>107</v>
+        <v>198</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>194</v>
+        <v>199</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>196</v>
-      </c>
-      <c r="O18" s="2"/>
+        <v>201</v>
+      </c>
+      <c r="O18" t="s" s="2">
+        <v>202</v>
+      </c>
       <c r="P18" t="s" s="2">
         <v>21</v>
       </c>
       <c r="Q18" s="2"/>
       <c r="R18" t="s" s="2">
-        <v>197</v>
+        <v>21</v>
       </c>
       <c r="S18" t="s" s="2">
         <v>21</v>
@@ -3803,13 +4011,13 @@
         <v>21</v>
       </c>
       <c r="X18" t="s" s="2">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="Y18" t="s" s="2">
-        <v>199</v>
+        <v>204</v>
       </c>
       <c r="Z18" t="s" s="2">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c r="AA18" t="s" s="2">
         <v>21</v>
@@ -3827,10 +4035,10 @@
         <v>21</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>193</v>
+        <v>206</v>
       </c>
       <c r="AG18" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="AH18" t="s" s="2">
         <v>87</v>
@@ -3842,35 +4050,35 @@
         <v>99</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>201</v>
+        <v>21</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>202</v>
+        <v>195</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>203</v>
+        <v>21</v>
       </c>
       <c r="AN18" t="s" s="2">
-        <v>21</v>
+        <v>207</v>
       </c>
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>204</v>
+        <v>209</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
-        <v>205</v>
+        <v>21</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G19" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="H19" t="s" s="2">
         <v>21</v>
@@ -3882,18 +4090,20 @@
         <v>88</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>206</v>
+        <v>101</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>209</v>
-      </c>
-      <c r="O19" s="2"/>
+        <v>212</v>
+      </c>
+      <c r="O19" t="s" s="2">
+        <v>213</v>
+      </c>
       <c r="P19" t="s" s="2">
         <v>21</v>
       </c>
@@ -3902,10 +4112,10 @@
         <v>21</v>
       </c>
       <c r="S19" t="s" s="2">
-        <v>21</v>
+        <v>214</v>
       </c>
       <c r="T19" t="s" s="2">
-        <v>21</v>
+        <v>215</v>
       </c>
       <c r="U19" t="s" s="2">
         <v>21</v>
@@ -3917,13 +4127,13 @@
         <v>21</v>
       </c>
       <c r="X19" t="s" s="2">
-        <v>210</v>
+        <v>21</v>
       </c>
       <c r="Y19" t="s" s="2">
-        <v>211</v>
+        <v>21</v>
       </c>
       <c r="Z19" t="s" s="2">
-        <v>212</v>
+        <v>21</v>
       </c>
       <c r="AA19" t="s" s="2">
         <v>21</v>
@@ -3941,7 +4151,7 @@
         <v>21</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>204</v>
+        <v>216</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>78</v>
@@ -3956,24 +4166,24 @@
         <v>99</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>213</v>
+        <v>21</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="AM19" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN19" t="s" s="2">
-        <v>21</v>
+        <v>218</v>
       </c>
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>215</v>
+        <v>220</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -3981,10 +4191,10 @@
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="H20" t="s" s="2">
         <v>21</v>
@@ -3996,15 +4206,17 @@
         <v>88</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>206</v>
+        <v>174</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>217</v>
-      </c>
-      <c r="N20" s="2"/>
+        <v>222</v>
+      </c>
+      <c r="N20" t="s" s="2">
+        <v>223</v>
+      </c>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
         <v>21</v>
@@ -4017,7 +4229,7 @@
         <v>21</v>
       </c>
       <c r="T20" t="s" s="2">
-        <v>21</v>
+        <v>224</v>
       </c>
       <c r="U20" t="s" s="2">
         <v>21</v>
@@ -4029,13 +4241,13 @@
         <v>21</v>
       </c>
       <c r="X20" t="s" s="2">
-        <v>210</v>
+        <v>21</v>
       </c>
       <c r="Y20" t="s" s="2">
-        <v>218</v>
+        <v>21</v>
       </c>
       <c r="Z20" t="s" s="2">
-        <v>219</v>
+        <v>21</v>
       </c>
       <c r="AA20" t="s" s="2">
         <v>21</v>
@@ -4053,7 +4265,7 @@
         <v>21</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>215</v>
+        <v>225</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>78</v>
@@ -4071,35 +4283,35 @@
         <v>21</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>220</v>
+        <v>226</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>221</v>
+        <v>21</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>21</v>
+        <v>227</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>222</v>
+        <v>228</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
-        <v>223</v>
+        <v>21</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="G21" t="s" s="2">
         <v>87</v>
       </c>
       <c r="H21" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="I21" t="s" s="2">
         <v>21</v>
@@ -4108,18 +4320,16 @@
         <v>88</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>206</v>
+        <v>230</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>224</v>
+        <v>231</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>225</v>
+        <v>232</v>
       </c>
       <c r="N21" s="2"/>
-      <c r="O21" t="s" s="2">
-        <v>226</v>
-      </c>
+      <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
         <v>21</v>
       </c>
@@ -4143,11 +4353,13 @@
         <v>21</v>
       </c>
       <c r="X21" t="s" s="2">
-        <v>198</v>
-      </c>
-      <c r="Y21" s="2"/>
+        <v>21</v>
+      </c>
+      <c r="Y21" t="s" s="2">
+        <v>21</v>
+      </c>
       <c r="Z21" t="s" s="2">
-        <v>227</v>
+        <v>21</v>
       </c>
       <c r="AA21" t="s" s="2">
         <v>21</v>
@@ -4165,7 +4377,7 @@
         <v>21</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>222</v>
+        <v>233</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>78</v>
@@ -4180,24 +4392,24 @@
         <v>99</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>228</v>
+        <v>21</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>230</v>
+        <v>21</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>231</v>
+        <v>235</v>
       </c>
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>232</v>
+        <v>237</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4217,18 +4429,20 @@
         <v>21</v>
       </c>
       <c r="J22" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>233</v>
+        <v>238</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>234</v>
+        <v>239</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>235</v>
-      </c>
-      <c r="N22" s="2"/>
+        <v>240</v>
+      </c>
+      <c r="N22" t="s" s="2">
+        <v>241</v>
+      </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
         <v>21</v>
@@ -4277,7 +4491,7 @@
         <v>21</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>236</v>
+        <v>242</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>78</v>
@@ -4289,38 +4503,38 @@
         <v>21</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>21</v>
+        <v>99</v>
       </c>
       <c r="AK22" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>237</v>
+        <v>243</v>
       </c>
       <c r="AM22" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>21</v>
+        <v>244</v>
       </c>
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>238</v>
+        <v>245</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>238</v>
+        <v>245</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
-        <v>151</v>
+        <v>21</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G23" t="s" s="2">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H23" t="s" s="2">
         <v>21</v>
@@ -4329,20 +4543,18 @@
         <v>21</v>
       </c>
       <c r="J23" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>132</v>
+        <v>246</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>239</v>
+        <v>247</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>240</v>
-      </c>
-      <c r="N23" t="s" s="2">
-        <v>154</v>
-      </c>
+        <v>248</v>
+      </c>
+      <c r="N23" s="2"/>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
         <v>21</v>
@@ -4379,19 +4591,19 @@
         <v>21</v>
       </c>
       <c r="AB23" t="s" s="2">
-        <v>135</v>
+        <v>21</v>
       </c>
       <c r="AC23" t="s" s="2">
-        <v>241</v>
+        <v>21</v>
       </c>
       <c r="AD23" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE23" t="s" s="2">
-        <v>136</v>
+        <v>21</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>78</v>
@@ -4403,13 +4615,13 @@
         <v>21</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>138</v>
+        <v>99</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>21</v>
+        <v>249</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>237</v>
+        <v>250</v>
       </c>
       <c r="AM23" t="s" s="2">
         <v>21</v>
@@ -4420,10 +4632,10 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>243</v>
+        <v>251</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>243</v>
+        <v>251</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4434,7 +4646,7 @@
         <v>78</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H24" t="s" s="2">
         <v>21</v>
@@ -4446,20 +4658,18 @@
         <v>88</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>244</v>
+        <v>101</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>245</v>
+        <v>252</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>246</v>
+        <v>253</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>247</v>
-      </c>
-      <c r="O24" t="s" s="2">
-        <v>248</v>
-      </c>
+        <v>254</v>
+      </c>
+      <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
         <v>21</v>
       </c>
@@ -4507,7 +4717,7 @@
         <v>21</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>78</v>
@@ -4522,7 +4732,7 @@
         <v>99</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>21</v>
+        <v>255</v>
       </c>
       <c r="AL24" t="s" s="2">
         <v>250</v>
@@ -4531,19 +4741,19 @@
         <v>21</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>251</v>
+        <v>21</v>
       </c>
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>21</v>
+        <v>257</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
@@ -4562,20 +4772,16 @@
         <v>88</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>233</v>
+        <v>258</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>253</v>
+        <v>259</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>254</v>
-      </c>
-      <c r="N25" t="s" s="2">
-        <v>255</v>
-      </c>
-      <c r="O25" t="s" s="2">
-        <v>256</v>
-      </c>
+        <v>260</v>
+      </c>
+      <c r="N25" s="2"/>
+      <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
         <v>21</v>
       </c>
@@ -4623,13 +4829,13 @@
         <v>21</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH25" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI25" t="s" s="2">
         <v>21</v>
@@ -4638,38 +4844,38 @@
         <v>99</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>21</v>
+        <v>261</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="AM25" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>259</v>
+        <v>21</v>
       </c>
     </row>
-    <row r="26">
+    <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="H26" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="I26" t="s" s="2">
         <v>21</v>
@@ -4678,15 +4884,17 @@
         <v>88</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>264</v>
-      </c>
-      <c r="N26" s="2"/>
+        <v>267</v>
+      </c>
+      <c r="N26" t="s" s="2">
+        <v>268</v>
+      </c>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
         <v>21</v>
@@ -4735,13 +4943,13 @@
         <v>21</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="AG26" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="AH26" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI26" t="s" s="2">
         <v>21</v>
@@ -4750,24 +4958,24 @@
         <v>99</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>267</v>
+        <v>21</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>268</v>
+        <v>21</v>
       </c>
     </row>
-    <row r="27" hidden="true">
+    <row r="27">
       <c r="A27" t="s" s="2">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4775,31 +4983,31 @@
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="H27" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="I27" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="J27" t="s" s="2">
         <v>88</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>270</v>
+        <v>107</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
@@ -4807,7 +5015,7 @@
       </c>
       <c r="Q27" s="2"/>
       <c r="R27" t="s" s="2">
-        <v>21</v>
+        <v>275</v>
       </c>
       <c r="S27" t="s" s="2">
         <v>21</v>
@@ -4825,13 +5033,13 @@
         <v>21</v>
       </c>
       <c r="X27" t="s" s="2">
-        <v>21</v>
+        <v>191</v>
       </c>
       <c r="Y27" t="s" s="2">
-        <v>21</v>
+        <v>276</v>
       </c>
       <c r="Z27" t="s" s="2">
-        <v>21</v>
+        <v>277</v>
       </c>
       <c r="AA27" t="s" s="2">
         <v>21</v>
@@ -4849,10 +5057,10 @@
         <v>21</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="AG27" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="AH27" t="s" s="2">
         <v>87</v>
@@ -4864,35 +5072,35 @@
         <v>99</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>277</v>
+        <v>21</v>
       </c>
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
-        <v>21</v>
+        <v>282</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="H28" t="s" s="2">
         <v>21</v>
@@ -4904,16 +5112,16 @@
         <v>88</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>279</v>
+        <v>198</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
@@ -4939,13 +5147,13 @@
         <v>21</v>
       </c>
       <c r="X28" t="s" s="2">
-        <v>21</v>
+        <v>286</v>
       </c>
       <c r="Y28" t="s" s="2">
-        <v>21</v>
+        <v>287</v>
       </c>
       <c r="Z28" t="s" s="2">
-        <v>21</v>
+        <v>288</v>
       </c>
       <c r="AA28" t="s" s="2">
         <v>21</v>
@@ -4963,7 +5171,7 @@
         <v>21</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>78</v>
@@ -4978,24 +5186,24 @@
         <v>99</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>283</v>
+        <v>289</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>284</v>
+        <v>290</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>285</v>
+        <v>21</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>286</v>
+        <v>21</v>
       </c>
     </row>
-    <row r="29">
+    <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5003,13 +5211,13 @@
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="H29" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="I29" t="s" s="2">
         <v>21</v>
@@ -5018,13 +5226,13 @@
         <v>88</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>288</v>
+        <v>198</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
@@ -5051,13 +5259,13 @@
         <v>21</v>
       </c>
       <c r="X29" t="s" s="2">
-        <v>21</v>
+        <v>286</v>
       </c>
       <c r="Y29" t="s" s="2">
-        <v>21</v>
+        <v>294</v>
       </c>
       <c r="Z29" t="s" s="2">
-        <v>21</v>
+        <v>295</v>
       </c>
       <c r="AA29" t="s" s="2">
         <v>21</v>
@@ -5075,7 +5283,7 @@
         <v>21</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>78</v>
@@ -5093,35 +5301,35 @@
         <v>21</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>291</v>
+        <v>296</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>292</v>
+        <v>297</v>
       </c>
       <c r="AN29" t="s" s="2">
         <v>21</v>
       </c>
     </row>
-    <row r="30" hidden="true">
+    <row r="30">
       <c r="A30" t="s" s="2">
-        <v>293</v>
+        <v>298</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>293</v>
+        <v>298</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
-        <v>21</v>
+        <v>299</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G30" t="s" s="2">
         <v>87</v>
       </c>
       <c r="H30" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="I30" t="s" s="2">
         <v>21</v>
@@ -5130,16 +5338,18 @@
         <v>88</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>294</v>
+        <v>198</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>295</v>
+        <v>300</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>296</v>
+        <v>301</v>
       </c>
       <c r="N30" s="2"/>
-      <c r="O30" s="2"/>
+      <c r="O30" t="s" s="2">
+        <v>302</v>
+      </c>
       <c r="P30" t="s" s="2">
         <v>21</v>
       </c>
@@ -5163,13 +5373,11 @@
         <v>21</v>
       </c>
       <c r="X30" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y30" t="s" s="2">
-        <v>21</v>
-      </c>
+        <v>191</v>
+      </c>
+      <c r="Y30" s="2"/>
       <c r="Z30" t="s" s="2">
-        <v>21</v>
+        <v>303</v>
       </c>
       <c r="AA30" t="s" s="2">
         <v>21</v>
@@ -5187,7 +5395,7 @@
         <v>21</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>293</v>
+        <v>298</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>78</v>
@@ -5202,24 +5410,24 @@
         <v>99</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>21</v>
+        <v>304</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>297</v>
+        <v>305</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>298</v>
+        <v>306</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>21</v>
+        <v>307</v>
       </c>
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>299</v>
+        <v>308</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>299</v>
+        <v>308</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5230,7 +5438,7 @@
         <v>78</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="H31" t="s" s="2">
         <v>21</v>
@@ -5239,16 +5447,16 @@
         <v>21</v>
       </c>
       <c r="J31" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>300</v>
+        <v>174</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>301</v>
+        <v>175</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>302</v>
+        <v>176</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -5299,25 +5507,25 @@
         <v>21</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>299</v>
+        <v>177</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH31" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI31" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>99</v>
+        <v>21</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>303</v>
+        <v>21</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>304</v>
+        <v>178</v>
       </c>
       <c r="AM31" t="s" s="2">
         <v>21</v>
@@ -5328,21 +5536,21 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>21</v>
+        <v>151</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H32" t="s" s="2">
         <v>21</v>
@@ -5354,15 +5562,17 @@
         <v>21</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>233</v>
+        <v>132</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>234</v>
+        <v>181</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>235</v>
-      </c>
-      <c r="N32" s="2"/>
+        <v>182</v>
+      </c>
+      <c r="N32" t="s" s="2">
+        <v>154</v>
+      </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
         <v>21</v>
@@ -5399,37 +5609,37 @@
         <v>21</v>
       </c>
       <c r="AB32" t="s" s="2">
-        <v>21</v>
+        <v>135</v>
       </c>
       <c r="AC32" t="s" s="2">
-        <v>21</v>
+        <v>183</v>
       </c>
       <c r="AD32" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE32" t="s" s="2">
-        <v>21</v>
+        <v>136</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>236</v>
+        <v>184</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI32" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>21</v>
+        <v>138</v>
       </c>
       <c r="AK32" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>237</v>
+        <v>178</v>
       </c>
       <c r="AM32" t="s" s="2">
         <v>21</v>
@@ -5440,14 +5650,14 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>151</v>
+        <v>21</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
@@ -5463,21 +5673,23 @@
         <v>21</v>
       </c>
       <c r="J33" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>132</v>
+        <v>311</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>239</v>
+        <v>312</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>240</v>
+        <v>313</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>154</v>
-      </c>
-      <c r="O33" s="2"/>
+        <v>314</v>
+      </c>
+      <c r="O33" t="s" s="2">
+        <v>315</v>
+      </c>
       <c r="P33" t="s" s="2">
         <v>21</v>
       </c>
@@ -5525,7 +5737,7 @@
         <v>21</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>242</v>
+        <v>316</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>78</v>
@@ -5537,62 +5749,62 @@
         <v>21</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>138</v>
+        <v>99</v>
       </c>
       <c r="AK33" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>237</v>
+        <v>317</v>
       </c>
       <c r="AM33" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>21</v>
+        <v>318</v>
       </c>
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>307</v>
+        <v>319</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>307</v>
+        <v>319</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
-        <v>308</v>
+        <v>21</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H34" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I34" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="J34" t="s" s="2">
         <v>88</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>132</v>
+        <v>174</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>309</v>
+        <v>320</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>310</v>
+        <v>321</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>154</v>
+        <v>322</v>
       </c>
       <c r="O34" t="s" s="2">
-        <v>155</v>
+        <v>323</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>21</v>
@@ -5641,53 +5853,53 @@
         <v>21</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>311</v>
+        <v>324</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH34" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI34" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>138</v>
+        <v>99</v>
       </c>
       <c r="AK34" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>130</v>
+        <v>325</v>
       </c>
       <c r="AM34" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>21</v>
+        <v>326</v>
       </c>
     </row>
-    <row r="35" hidden="true">
+    <row r="35">
       <c r="A35" t="s" s="2">
-        <v>312</v>
+        <v>327</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>312</v>
+        <v>327</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>21</v>
+        <v>328</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G35" t="s" s="2">
         <v>87</v>
       </c>
       <c r="H35" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="I35" t="s" s="2">
         <v>21</v>
@@ -5696,18 +5908,16 @@
         <v>88</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>206</v>
+        <v>329</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>313</v>
+        <v>330</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>314</v>
+        <v>331</v>
       </c>
       <c r="N35" s="2"/>
-      <c r="O35" t="s" s="2">
-        <v>315</v>
-      </c>
+      <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
         <v>21</v>
       </c>
@@ -5731,13 +5941,13 @@
         <v>21</v>
       </c>
       <c r="X35" t="s" s="2">
-        <v>210</v>
+        <v>21</v>
       </c>
       <c r="Y35" t="s" s="2">
-        <v>316</v>
+        <v>21</v>
       </c>
       <c r="Z35" t="s" s="2">
-        <v>317</v>
+        <v>21</v>
       </c>
       <c r="AA35" t="s" s="2">
         <v>21</v>
@@ -5755,10 +5965,10 @@
         <v>21</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>312</v>
+        <v>327</v>
       </c>
       <c r="AG35" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="AH35" t="s" s="2">
         <v>87</v>
@@ -5770,24 +5980,24 @@
         <v>99</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>318</v>
+        <v>332</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>319</v>
+        <v>333</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>21</v>
+        <v>334</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>320</v>
+        <v>335</v>
       </c>
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>321</v>
+        <v>336</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>321</v>
+        <v>336</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5795,10 +6005,10 @@
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="H36" t="s" s="2">
         <v>21</v>
@@ -5810,18 +6020,18 @@
         <v>88</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>322</v>
+        <v>337</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>323</v>
+        <v>338</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>324</v>
-      </c>
-      <c r="N36" s="2"/>
-      <c r="O36" t="s" s="2">
-        <v>325</v>
-      </c>
+        <v>339</v>
+      </c>
+      <c r="N36" t="s" s="2">
+        <v>340</v>
+      </c>
+      <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
         <v>21</v>
       </c>
@@ -5869,10 +6079,10 @@
         <v>21</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>321</v>
+        <v>336</v>
       </c>
       <c r="AG36" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="AH36" t="s" s="2">
         <v>87</v>
@@ -5884,24 +6094,24 @@
         <v>99</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>326</v>
+        <v>341</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>327</v>
+        <v>342</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>328</v>
+        <v>343</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>329</v>
+        <v>344</v>
       </c>
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>330</v>
+        <v>345</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>330</v>
+        <v>345</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5921,21 +6131,21 @@
         <v>21</v>
       </c>
       <c r="J37" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>331</v>
+        <v>346</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>332</v>
+        <v>347</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>333</v>
-      </c>
-      <c r="N37" s="2"/>
-      <c r="O37" t="s" s="2">
-        <v>334</v>
-      </c>
+        <v>348</v>
+      </c>
+      <c r="N37" t="s" s="2">
+        <v>349</v>
+      </c>
+      <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
         <v>21</v>
       </c>
@@ -5983,7 +6193,7 @@
         <v>21</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>330</v>
+        <v>345</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>78</v>
@@ -5998,24 +6208,24 @@
         <v>99</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>21</v>
+        <v>350</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>335</v>
+        <v>351</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>21</v>
+        <v>352</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>21</v>
+        <v>353</v>
       </c>
     </row>
-    <row r="38" hidden="true">
+    <row r="38">
       <c r="A38" t="s" s="2">
-        <v>336</v>
+        <v>354</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>336</v>
+        <v>354</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6023,13 +6233,13 @@
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="H38" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="I38" t="s" s="2">
         <v>21</v>
@@ -6038,18 +6248,16 @@
         <v>88</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>337</v>
+        <v>355</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>338</v>
+        <v>356</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>339</v>
+        <v>357</v>
       </c>
       <c r="N38" s="2"/>
-      <c r="O38" t="s" s="2">
-        <v>340</v>
-      </c>
+      <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
         <v>21</v>
       </c>
@@ -6097,7 +6305,7 @@
         <v>21</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>336</v>
+        <v>354</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>78</v>
@@ -6115,10 +6323,10 @@
         <v>21</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>341</v>
+        <v>358</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>342</v>
+        <v>359</v>
       </c>
       <c r="AN38" t="s" s="2">
         <v>21</v>
@@ -6126,10 +6334,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>343</v>
+        <v>360</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>343</v>
+        <v>360</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6140,7 +6348,7 @@
         <v>78</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="H39" t="s" s="2">
         <v>21</v>
@@ -6152,17 +6360,15 @@
         <v>88</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>206</v>
+        <v>361</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>344</v>
+        <v>362</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>345</v>
-      </c>
-      <c r="N39" t="s" s="2">
-        <v>346</v>
-      </c>
+        <v>363</v>
+      </c>
+      <c r="N39" s="2"/>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
         <v>21</v>
@@ -6187,13 +6393,13 @@
         <v>21</v>
       </c>
       <c r="X39" t="s" s="2">
-        <v>210</v>
+        <v>21</v>
       </c>
       <c r="Y39" t="s" s="2">
-        <v>347</v>
+        <v>21</v>
       </c>
       <c r="Z39" t="s" s="2">
-        <v>348</v>
+        <v>21</v>
       </c>
       <c r="AA39" t="s" s="2">
         <v>21</v>
@@ -6211,13 +6417,13 @@
         <v>21</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>343</v>
+        <v>360</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH39" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI39" t="s" s="2">
         <v>21</v>
@@ -6226,13 +6432,13 @@
         <v>99</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>349</v>
+        <v>21</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>350</v>
+        <v>364</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>351</v>
+        <v>365</v>
       </c>
       <c r="AN39" t="s" s="2">
         <v>21</v>
@@ -6240,10 +6446,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>352</v>
+        <v>366</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>352</v>
+        <v>366</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6266,17 +6472,15 @@
         <v>88</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>353</v>
+        <v>367</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>354</v>
+        <v>368</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>355</v>
-      </c>
-      <c r="N40" t="s" s="2">
-        <v>356</v>
-      </c>
+        <v>369</v>
+      </c>
+      <c r="N40" s="2"/>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
         <v>21</v>
@@ -6325,7 +6529,7 @@
         <v>21</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>352</v>
+        <v>366</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>78</v>
@@ -6340,13 +6544,13 @@
         <v>99</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>357</v>
+        <v>370</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>350</v>
+        <v>371</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>351</v>
+        <v>21</v>
       </c>
       <c r="AN40" t="s" s="2">
         <v>21</v>
@@ -6354,10 +6558,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>358</v>
+        <v>372</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>358</v>
+        <v>372</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6368,7 +6572,7 @@
         <v>78</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="H41" t="s" s="2">
         <v>21</v>
@@ -6377,20 +6581,18 @@
         <v>21</v>
       </c>
       <c r="J41" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>206</v>
+        <v>174</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>359</v>
+        <v>175</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>360</v>
-      </c>
-      <c r="N41" t="s" s="2">
-        <v>361</v>
-      </c>
+        <v>176</v>
+      </c>
+      <c r="N41" s="2"/>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
         <v>21</v>
@@ -6415,13 +6617,13 @@
         <v>21</v>
       </c>
       <c r="X41" t="s" s="2">
-        <v>210</v>
+        <v>21</v>
       </c>
       <c r="Y41" t="s" s="2">
-        <v>362</v>
+        <v>21</v>
       </c>
       <c r="Z41" t="s" s="2">
-        <v>363</v>
+        <v>21</v>
       </c>
       <c r="AA41" t="s" s="2">
         <v>21</v>
@@ -6439,50 +6641,50 @@
         <v>21</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>358</v>
+        <v>177</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI41" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>99</v>
+        <v>21</v>
       </c>
       <c r="AK41" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>364</v>
+        <v>178</v>
       </c>
       <c r="AM41" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>365</v>
+        <v>21</v>
       </c>
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>366</v>
+        <v>373</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>366</v>
+        <v>373</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>21</v>
+        <v>151</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H42" t="s" s="2">
         <v>21</v>
@@ -6491,19 +6693,19 @@
         <v>21</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>206</v>
+        <v>132</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>367</v>
+        <v>181</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>368</v>
+        <v>182</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>369</v>
+        <v>154</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -6529,13 +6731,13 @@
         <v>21</v>
       </c>
       <c r="X42" t="s" s="2">
-        <v>210</v>
+        <v>21</v>
       </c>
       <c r="Y42" t="s" s="2">
-        <v>370</v>
+        <v>21</v>
       </c>
       <c r="Z42" t="s" s="2">
-        <v>371</v>
+        <v>21</v>
       </c>
       <c r="AA42" t="s" s="2">
         <v>21</v>
@@ -6553,25 +6755,25 @@
         <v>21</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>366</v>
+        <v>184</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI42" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="AK42" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>372</v>
+        <v>178</v>
       </c>
       <c r="AM42" t="s" s="2">
         <v>21</v>
@@ -6582,14 +6784,14 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>21</v>
+        <v>375</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
@@ -6602,24 +6804,26 @@
         <v>21</v>
       </c>
       <c r="I43" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="J43" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>374</v>
+        <v>132</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>377</v>
-      </c>
-      <c r="O43" s="2"/>
+        <v>154</v>
+      </c>
+      <c r="O43" t="s" s="2">
+        <v>155</v>
+      </c>
       <c r="P43" t="s" s="2">
         <v>21</v>
       </c>
@@ -6667,7 +6871,7 @@
         <v>21</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>373</v>
+        <v>378</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>78</v>
@@ -6679,13 +6883,13 @@
         <v>21</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="AK43" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>378</v>
+        <v>130</v>
       </c>
       <c r="AM43" t="s" s="2">
         <v>21</v>
@@ -6710,7 +6914,7 @@
         <v>78</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="H44" t="s" s="2">
         <v>21</v>
@@ -6719,10 +6923,10 @@
         <v>21</v>
       </c>
       <c r="J44" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>206</v>
+        <v>198</v>
       </c>
       <c r="L44" t="s" s="2">
         <v>380</v>
@@ -6730,10 +6934,10 @@
       <c r="M44" t="s" s="2">
         <v>381</v>
       </c>
-      <c r="N44" t="s" s="2">
+      <c r="N44" s="2"/>
+      <c r="O44" t="s" s="2">
         <v>382</v>
       </c>
-      <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
         <v>21</v>
       </c>
@@ -6757,7 +6961,7 @@
         <v>21</v>
       </c>
       <c r="X44" t="s" s="2">
-        <v>210</v>
+        <v>286</v>
       </c>
       <c r="Y44" t="s" s="2">
         <v>383</v>
@@ -6787,7 +6991,7 @@
         <v>78</v>
       </c>
       <c r="AH44" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI44" t="s" s="2">
         <v>21</v>
@@ -6796,24 +7000,24 @@
         <v>99</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>21</v>
+        <v>385</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="AM44" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>21</v>
+        <v>387</v>
       </c>
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6821,10 +7025,10 @@
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="H45" t="s" s="2">
         <v>21</v>
@@ -6833,20 +7037,20 @@
         <v>21</v>
       </c>
       <c r="J45" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" t="s" s="2">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>21</v>
@@ -6895,13 +7099,13 @@
         <v>21</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="AG45" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI45" t="s" s="2">
         <v>21</v>
@@ -6910,24 +7114,24 @@
         <v>99</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>21</v>
+        <v>393</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>385</v>
+        <v>394</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>21</v>
+        <v>395</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>21</v>
+        <v>396</v>
       </c>
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>391</v>
+        <v>397</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>391</v>
+        <v>397</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -6938,7 +7142,7 @@
         <v>78</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="H46" t="s" s="2">
         <v>21</v>
@@ -6950,16 +7154,18 @@
         <v>21</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>206</v>
+        <v>238</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>392</v>
+        <v>398</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>393</v>
+        <v>399</v>
       </c>
       <c r="N46" s="2"/>
-      <c r="O46" s="2"/>
+      <c r="O46" t="s" s="2">
+        <v>400</v>
+      </c>
       <c r="P46" t="s" s="2">
         <v>21</v>
       </c>
@@ -6983,13 +7189,13 @@
         <v>21</v>
       </c>
       <c r="X46" t="s" s="2">
-        <v>210</v>
+        <v>21</v>
       </c>
       <c r="Y46" t="s" s="2">
-        <v>394</v>
+        <v>21</v>
       </c>
       <c r="Z46" t="s" s="2">
-        <v>395</v>
+        <v>21</v>
       </c>
       <c r="AA46" t="s" s="2">
         <v>21</v>
@@ -7007,13 +7213,13 @@
         <v>21</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>391</v>
+        <v>397</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH46" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI46" t="s" s="2">
         <v>21</v>
@@ -7025,7 +7231,7 @@
         <v>21</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>396</v>
+        <v>401</v>
       </c>
       <c r="AM46" t="s" s="2">
         <v>21</v>
@@ -7036,10 +7242,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>397</v>
+        <v>402</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>397</v>
+        <v>402</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7050,7 +7256,7 @@
         <v>78</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="H47" t="s" s="2">
         <v>21</v>
@@ -7059,19 +7265,21 @@
         <v>21</v>
       </c>
       <c r="J47" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>399</v>
+        <v>404</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>400</v>
+        <v>405</v>
       </c>
       <c r="N47" s="2"/>
-      <c r="O47" s="2"/>
+      <c r="O47" t="s" s="2">
+        <v>406</v>
+      </c>
       <c r="P47" t="s" s="2">
         <v>21</v>
       </c>
@@ -7119,13 +7327,13 @@
         <v>21</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>397</v>
+        <v>402</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH47" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI47" t="s" s="2">
         <v>21</v>
@@ -7134,24 +7342,24 @@
         <v>99</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>401</v>
+        <v>21</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>402</v>
+        <v>407</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>21</v>
+        <v>408</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>403</v>
+        <v>21</v>
       </c>
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>404</v>
+        <v>409</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>404</v>
+        <v>409</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7162,7 +7370,7 @@
         <v>78</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="H48" t="s" s="2">
         <v>21</v>
@@ -7171,18 +7379,20 @@
         <v>21</v>
       </c>
       <c r="J48" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>233</v>
+        <v>198</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>234</v>
+        <v>410</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>235</v>
-      </c>
-      <c r="N48" s="2"/>
+        <v>411</v>
+      </c>
+      <c r="N48" t="s" s="2">
+        <v>412</v>
+      </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
         <v>21</v>
@@ -7207,13 +7417,13 @@
         <v>21</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>21</v>
+        <v>286</v>
       </c>
       <c r="Y48" t="s" s="2">
-        <v>21</v>
+        <v>413</v>
       </c>
       <c r="Z48" t="s" s="2">
-        <v>21</v>
+        <v>414</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>21</v>
@@ -7231,28 +7441,28 @@
         <v>21</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>236</v>
+        <v>409</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH48" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI48" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>21</v>
+        <v>99</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>21</v>
+        <v>415</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>237</v>
+        <v>416</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>21</v>
+        <v>417</v>
       </c>
       <c r="AN48" t="s" s="2">
         <v>21</v>
@@ -7260,21 +7470,21 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>405</v>
+        <v>418</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>405</v>
+        <v>418</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
-        <v>151</v>
+        <v>21</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H49" t="s" s="2">
         <v>21</v>
@@ -7283,19 +7493,19 @@
         <v>21</v>
       </c>
       <c r="J49" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>132</v>
+        <v>419</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>239</v>
+        <v>420</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>240</v>
+        <v>421</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>154</v>
+        <v>422</v>
       </c>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
@@ -7333,19 +7543,19 @@
         <v>21</v>
       </c>
       <c r="AB49" t="s" s="2">
-        <v>135</v>
+        <v>21</v>
       </c>
       <c r="AC49" t="s" s="2">
-        <v>241</v>
+        <v>21</v>
       </c>
       <c r="AD49" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE49" t="s" s="2">
-        <v>136</v>
+        <v>21</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>242</v>
+        <v>418</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>78</v>
@@ -7357,16 +7567,16 @@
         <v>21</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>138</v>
+        <v>99</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>21</v>
+        <v>423</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>237</v>
+        <v>416</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>21</v>
+        <v>417</v>
       </c>
       <c r="AN49" t="s" s="2">
         <v>21</v>
@@ -7374,10 +7584,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>406</v>
+        <v>424</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>406</v>
+        <v>424</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7400,16 +7610,16 @@
         <v>88</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>407</v>
+        <v>198</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>408</v>
+        <v>425</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>409</v>
+        <v>426</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>410</v>
+        <v>427</v>
       </c>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
@@ -7435,13 +7645,13 @@
         <v>21</v>
       </c>
       <c r="X50" t="s" s="2">
-        <v>21</v>
+        <v>286</v>
       </c>
       <c r="Y50" t="s" s="2">
-        <v>21</v>
+        <v>428</v>
       </c>
       <c r="Z50" t="s" s="2">
-        <v>21</v>
+        <v>429</v>
       </c>
       <c r="AA50" t="s" s="2">
         <v>21</v>
@@ -7459,13 +7669,13 @@
         <v>21</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>411</v>
+        <v>424</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI50" t="s" s="2">
         <v>21</v>
@@ -7477,21 +7687,21 @@
         <v>21</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>412</v>
+        <v>430</v>
       </c>
       <c r="AM50" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>130</v>
+        <v>431</v>
       </c>
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>413</v>
+        <v>432</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>413</v>
+        <v>432</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7514,15 +7724,17 @@
         <v>88</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>279</v>
+        <v>198</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>414</v>
+        <v>433</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>415</v>
-      </c>
-      <c r="N51" s="2"/>
+        <v>434</v>
+      </c>
+      <c r="N51" t="s" s="2">
+        <v>435</v>
+      </c>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
         <v>21</v>
@@ -7547,13 +7759,13 @@
         <v>21</v>
       </c>
       <c r="X51" t="s" s="2">
-        <v>21</v>
+        <v>286</v>
       </c>
       <c r="Y51" t="s" s="2">
-        <v>21</v>
+        <v>436</v>
       </c>
       <c r="Z51" t="s" s="2">
-        <v>21</v>
+        <v>437</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>21</v>
@@ -7571,7 +7783,7 @@
         <v>21</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>416</v>
+        <v>432</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>78</v>
@@ -7589,21 +7801,21 @@
         <v>21</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>417</v>
+        <v>438</v>
       </c>
       <c r="AM51" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>130</v>
+        <v>21</v>
       </c>
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>418</v>
+        <v>439</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>418</v>
+        <v>439</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7611,10 +7823,10 @@
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H52" t="s" s="2">
         <v>21</v>
@@ -7623,18 +7835,20 @@
         <v>21</v>
       </c>
       <c r="J52" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>419</v>
+        <v>440</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>420</v>
+        <v>441</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>421</v>
-      </c>
-      <c r="N52" s="2"/>
+        <v>442</v>
+      </c>
+      <c r="N52" t="s" s="2">
+        <v>443</v>
+      </c>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
         <v>21</v>
@@ -7683,13 +7897,13 @@
         <v>21</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>422</v>
+        <v>439</v>
       </c>
       <c r="AG52" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="AH52" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI52" t="s" s="2">
         <v>21</v>
@@ -7701,21 +7915,21 @@
         <v>21</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>423</v>
+        <v>444</v>
       </c>
       <c r="AM52" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>130</v>
+        <v>21</v>
       </c>
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>424</v>
+        <v>445</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>424</v>
+        <v>445</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7738,15 +7952,17 @@
         <v>21</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>300</v>
+        <v>198</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>425</v>
+        <v>446</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>426</v>
-      </c>
-      <c r="N53" s="2"/>
+        <v>447</v>
+      </c>
+      <c r="N53" t="s" s="2">
+        <v>448</v>
+      </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
         <v>21</v>
@@ -7771,13 +7987,13 @@
         <v>21</v>
       </c>
       <c r="X53" t="s" s="2">
-        <v>21</v>
+        <v>286</v>
       </c>
       <c r="Y53" t="s" s="2">
-        <v>21</v>
+        <v>449</v>
       </c>
       <c r="Z53" t="s" s="2">
-        <v>21</v>
+        <v>450</v>
       </c>
       <c r="AA53" t="s" s="2">
         <v>21</v>
@@ -7795,7 +8011,7 @@
         <v>21</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>424</v>
+        <v>445</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>78</v>
@@ -7813,7 +8029,7 @@
         <v>21</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>427</v>
+        <v>451</v>
       </c>
       <c r="AM53" t="s" s="2">
         <v>21</v>
@@ -7824,10 +8040,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>428</v>
+        <v>452</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>428</v>
+        <v>452</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -7838,7 +8054,7 @@
         <v>78</v>
       </c>
       <c r="G54" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="H54" t="s" s="2">
         <v>21</v>
@@ -7850,16 +8066,18 @@
         <v>21</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>233</v>
+        <v>453</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>234</v>
+        <v>454</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>235</v>
+        <v>455</v>
       </c>
       <c r="N54" s="2"/>
-      <c r="O54" s="2"/>
+      <c r="O54" t="s" s="2">
+        <v>456</v>
+      </c>
       <c r="P54" t="s" s="2">
         <v>21</v>
       </c>
@@ -7907,25 +8125,25 @@
         <v>21</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>236</v>
+        <v>452</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH54" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI54" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>21</v>
+        <v>99</v>
       </c>
       <c r="AK54" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>237</v>
+        <v>451</v>
       </c>
       <c r="AM54" t="s" s="2">
         <v>21</v>
@@ -7936,21 +8154,21 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>429</v>
+        <v>457</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>429</v>
+        <v>457</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>151</v>
+        <v>21</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G55" t="s" s="2">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H55" t="s" s="2">
         <v>21</v>
@@ -7962,17 +8180,15 @@
         <v>21</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>132</v>
+        <v>198</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>239</v>
+        <v>458</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>240</v>
-      </c>
-      <c r="N55" t="s" s="2">
-        <v>154</v>
-      </c>
+        <v>459</v>
+      </c>
+      <c r="N55" s="2"/>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
         <v>21</v>
@@ -7997,13 +8213,13 @@
         <v>21</v>
       </c>
       <c r="X55" t="s" s="2">
-        <v>21</v>
+        <v>286</v>
       </c>
       <c r="Y55" t="s" s="2">
-        <v>21</v>
+        <v>460</v>
       </c>
       <c r="Z55" t="s" s="2">
-        <v>21</v>
+        <v>461</v>
       </c>
       <c r="AA55" t="s" s="2">
         <v>21</v>
@@ -8021,7 +8237,7 @@
         <v>21</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>242</v>
+        <v>457</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>78</v>
@@ -8033,13 +8249,13 @@
         <v>21</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>138</v>
+        <v>99</v>
       </c>
       <c r="AK55" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>237</v>
+        <v>462</v>
       </c>
       <c r="AM55" t="s" s="2">
         <v>21</v>
@@ -8050,46 +8266,42 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>430</v>
+        <v>463</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>430</v>
+        <v>463</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
-        <v>308</v>
+        <v>21</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G56" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H56" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I56" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="J56" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>132</v>
+        <v>464</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>309</v>
+        <v>465</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>310</v>
-      </c>
-      <c r="N56" t="s" s="2">
-        <v>154</v>
-      </c>
-      <c r="O56" t="s" s="2">
-        <v>155</v>
-      </c>
+        <v>466</v>
+      </c>
+      <c r="N56" s="2"/>
+      <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
         <v>21</v>
       </c>
@@ -8137,7 +8349,7 @@
         <v>21</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>311</v>
+        <v>463</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>78</v>
@@ -8149,27 +8361,27 @@
         <v>21</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>138</v>
+        <v>99</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>21</v>
+        <v>467</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>130</v>
+        <v>468</v>
       </c>
       <c r="AM56" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>21</v>
+        <v>469</v>
       </c>
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>431</v>
+        <v>470</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>431</v>
+        <v>470</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8192,13 +8404,13 @@
         <v>21</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>206</v>
+        <v>174</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>432</v>
+        <v>175</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>433</v>
+        <v>176</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
@@ -8225,13 +8437,13 @@
         <v>21</v>
       </c>
       <c r="X57" t="s" s="2">
-        <v>111</v>
+        <v>21</v>
       </c>
       <c r="Y57" t="s" s="2">
-        <v>434</v>
+        <v>21</v>
       </c>
       <c r="Z57" t="s" s="2">
-        <v>435</v>
+        <v>21</v>
       </c>
       <c r="AA57" t="s" s="2">
         <v>21</v>
@@ -8249,7 +8461,7 @@
         <v>21</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>431</v>
+        <v>177</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>78</v>
@@ -8261,13 +8473,13 @@
         <v>21</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>99</v>
+        <v>21</v>
       </c>
       <c r="AK57" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>436</v>
+        <v>178</v>
       </c>
       <c r="AM57" t="s" s="2">
         <v>21</v>
@@ -8278,21 +8490,21 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>437</v>
+        <v>471</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>437</v>
+        <v>471</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
-        <v>21</v>
+        <v>151</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="G58" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H58" t="s" s="2">
         <v>21</v>
@@ -8304,15 +8516,17 @@
         <v>21</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>438</v>
+        <v>132</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>439</v>
+        <v>181</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>440</v>
-      </c>
-      <c r="N58" s="2"/>
+        <v>182</v>
+      </c>
+      <c r="N58" t="s" s="2">
+        <v>154</v>
+      </c>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
         <v>21</v>
@@ -8349,37 +8563,37 @@
         <v>21</v>
       </c>
       <c r="AB58" t="s" s="2">
-        <v>21</v>
+        <v>135</v>
       </c>
       <c r="AC58" t="s" s="2">
-        <v>21</v>
+        <v>183</v>
       </c>
       <c r="AD58" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE58" t="s" s="2">
-        <v>21</v>
+        <v>136</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>437</v>
+        <v>184</v>
       </c>
       <c r="AG58" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="AH58" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI58" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="AK58" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>441</v>
+        <v>178</v>
       </c>
       <c r="AM58" t="s" s="2">
         <v>21</v>
@@ -8390,10 +8604,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>442</v>
+        <v>472</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>442</v>
+        <v>472</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8413,23 +8627,21 @@
         <v>21</v>
       </c>
       <c r="J59" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>443</v>
+        <v>473</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>444</v>
+        <v>474</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>445</v>
+        <v>475</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>446</v>
-      </c>
-      <c r="O59" t="s" s="2">
-        <v>447</v>
-      </c>
+        <v>476</v>
+      </c>
+      <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
         <v>21</v>
       </c>
@@ -8477,13 +8689,13 @@
         <v>21</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>442</v>
+        <v>477</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH59" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI59" t="s" s="2">
         <v>21</v>
@@ -8495,21 +8707,21 @@
         <v>21</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>448</v>
+        <v>478</v>
       </c>
       <c r="AM59" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>21</v>
+        <v>130</v>
       </c>
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>449</v>
+        <v>479</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>449</v>
+        <v>479</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8529,20 +8741,18 @@
         <v>21</v>
       </c>
       <c r="J60" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>206</v>
+        <v>346</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>450</v>
+        <v>480</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>451</v>
-      </c>
-      <c r="N60" t="s" s="2">
-        <v>446</v>
-      </c>
+        <v>481</v>
+      </c>
+      <c r="N60" s="2"/>
       <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
         <v>21</v>
@@ -8567,13 +8777,13 @@
         <v>21</v>
       </c>
       <c r="X60" t="s" s="2">
-        <v>210</v>
+        <v>21</v>
       </c>
       <c r="Y60" t="s" s="2">
-        <v>452</v>
+        <v>21</v>
       </c>
       <c r="Z60" t="s" s="2">
-        <v>453</v>
+        <v>21</v>
       </c>
       <c r="AA60" t="s" s="2">
         <v>21</v>
@@ -8591,13 +8801,13 @@
         <v>21</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>449</v>
+        <v>482</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH60" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI60" t="s" s="2">
         <v>21</v>
@@ -8609,17 +8819,1037 @@
         <v>21</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>454</v>
+        <v>483</v>
       </c>
       <c r="AM60" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN60" t="s" s="2">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="61" hidden="true">
+      <c r="A61" t="s" s="2">
+        <v>484</v>
+      </c>
+      <c r="B61" t="s" s="2">
+        <v>484</v>
+      </c>
+      <c r="C61" s="2"/>
+      <c r="D61" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E61" s="2"/>
+      <c r="F61" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="G61" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H61" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I61" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J61" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="K61" t="s" s="2">
+        <v>485</v>
+      </c>
+      <c r="L61" t="s" s="2">
+        <v>486</v>
+      </c>
+      <c r="M61" t="s" s="2">
+        <v>487</v>
+      </c>
+      <c r="N61" s="2"/>
+      <c r="O61" s="2"/>
+      <c r="P61" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q61" s="2"/>
+      <c r="R61" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S61" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T61" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U61" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V61" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W61" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X61" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y61" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z61" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA61" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB61" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC61" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD61" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE61" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF61" t="s" s="2">
+        <v>488</v>
+      </c>
+      <c r="AG61" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AH61" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI61" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ61" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK61" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL61" t="s" s="2">
+        <v>489</v>
+      </c>
+      <c r="AM61" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN61" t="s" s="2">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="62" hidden="true">
+      <c r="A62" t="s" s="2">
+        <v>490</v>
+      </c>
+      <c r="B62" t="s" s="2">
+        <v>490</v>
+      </c>
+      <c r="C62" s="2"/>
+      <c r="D62" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E62" s="2"/>
+      <c r="F62" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G62" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H62" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I62" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J62" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K62" t="s" s="2">
+        <v>367</v>
+      </c>
+      <c r="L62" t="s" s="2">
+        <v>491</v>
+      </c>
+      <c r="M62" t="s" s="2">
+        <v>492</v>
+      </c>
+      <c r="N62" s="2"/>
+      <c r="O62" s="2"/>
+      <c r="P62" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q62" s="2"/>
+      <c r="R62" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S62" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T62" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U62" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V62" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W62" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X62" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y62" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z62" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA62" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB62" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC62" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD62" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE62" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF62" t="s" s="2">
+        <v>490</v>
+      </c>
+      <c r="AG62" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH62" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI62" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ62" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK62" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL62" t="s" s="2">
+        <v>493</v>
+      </c>
+      <c r="AM62" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN62" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="63" hidden="true">
+      <c r="A63" t="s" s="2">
+        <v>494</v>
+      </c>
+      <c r="B63" t="s" s="2">
+        <v>494</v>
+      </c>
+      <c r="C63" s="2"/>
+      <c r="D63" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E63" s="2"/>
+      <c r="F63" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G63" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H63" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I63" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J63" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K63" t="s" s="2">
+        <v>174</v>
+      </c>
+      <c r="L63" t="s" s="2">
+        <v>175</v>
+      </c>
+      <c r="M63" t="s" s="2">
+        <v>176</v>
+      </c>
+      <c r="N63" s="2"/>
+      <c r="O63" s="2"/>
+      <c r="P63" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q63" s="2"/>
+      <c r="R63" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S63" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T63" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U63" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V63" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W63" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X63" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y63" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z63" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA63" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB63" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC63" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD63" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE63" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF63" t="s" s="2">
+        <v>177</v>
+      </c>
+      <c r="AG63" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH63" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI63" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ63" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AK63" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL63" t="s" s="2">
+        <v>178</v>
+      </c>
+      <c r="AM63" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN63" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="64" hidden="true">
+      <c r="A64" t="s" s="2">
+        <v>495</v>
+      </c>
+      <c r="B64" t="s" s="2">
+        <v>495</v>
+      </c>
+      <c r="C64" s="2"/>
+      <c r="D64" t="s" s="2">
+        <v>151</v>
+      </c>
+      <c r="E64" s="2"/>
+      <c r="F64" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G64" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H64" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I64" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J64" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K64" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="L64" t="s" s="2">
+        <v>181</v>
+      </c>
+      <c r="M64" t="s" s="2">
+        <v>182</v>
+      </c>
+      <c r="N64" t="s" s="2">
+        <v>154</v>
+      </c>
+      <c r="O64" s="2"/>
+      <c r="P64" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q64" s="2"/>
+      <c r="R64" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S64" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T64" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U64" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V64" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W64" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X64" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y64" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z64" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA64" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB64" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC64" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD64" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE64" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF64" t="s" s="2">
+        <v>184</v>
+      </c>
+      <c r="AG64" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH64" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI64" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ64" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="AK64" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL64" t="s" s="2">
+        <v>178</v>
+      </c>
+      <c r="AM64" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN64" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="65" hidden="true">
+      <c r="A65" t="s" s="2">
+        <v>496</v>
+      </c>
+      <c r="B65" t="s" s="2">
+        <v>496</v>
+      </c>
+      <c r="C65" s="2"/>
+      <c r="D65" t="s" s="2">
+        <v>375</v>
+      </c>
+      <c r="E65" s="2"/>
+      <c r="F65" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G65" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H65" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I65" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="J65" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="K65" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="L65" t="s" s="2">
+        <v>376</v>
+      </c>
+      <c r="M65" t="s" s="2">
+        <v>377</v>
+      </c>
+      <c r="N65" t="s" s="2">
+        <v>154</v>
+      </c>
+      <c r="O65" t="s" s="2">
+        <v>155</v>
+      </c>
+      <c r="P65" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q65" s="2"/>
+      <c r="R65" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S65" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T65" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U65" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V65" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W65" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X65" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y65" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z65" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA65" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB65" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC65" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD65" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE65" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF65" t="s" s="2">
+        <v>378</v>
+      </c>
+      <c r="AG65" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH65" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI65" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ65" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="AK65" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL65" t="s" s="2">
+        <v>130</v>
+      </c>
+      <c r="AM65" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN65" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="66" hidden="true">
+      <c r="A66" t="s" s="2">
+        <v>497</v>
+      </c>
+      <c r="B66" t="s" s="2">
+        <v>497</v>
+      </c>
+      <c r="C66" s="2"/>
+      <c r="D66" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E66" s="2"/>
+      <c r="F66" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G66" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H66" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I66" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J66" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K66" t="s" s="2">
+        <v>198</v>
+      </c>
+      <c r="L66" t="s" s="2">
+        <v>498</v>
+      </c>
+      <c r="M66" t="s" s="2">
+        <v>499</v>
+      </c>
+      <c r="N66" s="2"/>
+      <c r="O66" s="2"/>
+      <c r="P66" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q66" s="2"/>
+      <c r="R66" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S66" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T66" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U66" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V66" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W66" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X66" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="Y66" t="s" s="2">
+        <v>500</v>
+      </c>
+      <c r="Z66" t="s" s="2">
+        <v>501</v>
+      </c>
+      <c r="AA66" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB66" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC66" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD66" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE66" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF66" t="s" s="2">
+        <v>497</v>
+      </c>
+      <c r="AG66" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH66" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI66" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ66" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK66" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL66" t="s" s="2">
+        <v>502</v>
+      </c>
+      <c r="AM66" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN66" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="67" hidden="true">
+      <c r="A67" t="s" s="2">
+        <v>503</v>
+      </c>
+      <c r="B67" t="s" s="2">
+        <v>503</v>
+      </c>
+      <c r="C67" s="2"/>
+      <c r="D67" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E67" s="2"/>
+      <c r="F67" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="G67" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H67" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I67" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J67" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K67" t="s" s="2">
+        <v>504</v>
+      </c>
+      <c r="L67" t="s" s="2">
+        <v>505</v>
+      </c>
+      <c r="M67" t="s" s="2">
+        <v>506</v>
+      </c>
+      <c r="N67" s="2"/>
+      <c r="O67" s="2"/>
+      <c r="P67" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q67" s="2"/>
+      <c r="R67" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S67" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T67" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U67" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V67" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W67" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X67" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y67" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z67" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA67" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB67" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC67" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD67" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE67" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF67" t="s" s="2">
+        <v>503</v>
+      </c>
+      <c r="AG67" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AH67" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI67" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ67" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK67" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL67" t="s" s="2">
+        <v>507</v>
+      </c>
+      <c r="AM67" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN67" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="68" hidden="true">
+      <c r="A68" t="s" s="2">
+        <v>508</v>
+      </c>
+      <c r="B68" t="s" s="2">
+        <v>508</v>
+      </c>
+      <c r="C68" s="2"/>
+      <c r="D68" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E68" s="2"/>
+      <c r="F68" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G68" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H68" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I68" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J68" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K68" t="s" s="2">
+        <v>509</v>
+      </c>
+      <c r="L68" t="s" s="2">
+        <v>510</v>
+      </c>
+      <c r="M68" t="s" s="2">
+        <v>511</v>
+      </c>
+      <c r="N68" t="s" s="2">
+        <v>512</v>
+      </c>
+      <c r="O68" t="s" s="2">
+        <v>513</v>
+      </c>
+      <c r="P68" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q68" s="2"/>
+      <c r="R68" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S68" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T68" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U68" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V68" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W68" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X68" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y68" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z68" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA68" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB68" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC68" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD68" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE68" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF68" t="s" s="2">
+        <v>508</v>
+      </c>
+      <c r="AG68" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH68" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI68" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ68" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK68" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL68" t="s" s="2">
+        <v>514</v>
+      </c>
+      <c r="AM68" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN68" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="69" hidden="true">
+      <c r="A69" t="s" s="2">
+        <v>515</v>
+      </c>
+      <c r="B69" t="s" s="2">
+        <v>515</v>
+      </c>
+      <c r="C69" s="2"/>
+      <c r="D69" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E69" s="2"/>
+      <c r="F69" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G69" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H69" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I69" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J69" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K69" t="s" s="2">
+        <v>198</v>
+      </c>
+      <c r="L69" t="s" s="2">
+        <v>516</v>
+      </c>
+      <c r="M69" t="s" s="2">
+        <v>517</v>
+      </c>
+      <c r="N69" t="s" s="2">
+        <v>512</v>
+      </c>
+      <c r="O69" s="2"/>
+      <c r="P69" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q69" s="2"/>
+      <c r="R69" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S69" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T69" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U69" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V69" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W69" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X69" t="s" s="2">
+        <v>286</v>
+      </c>
+      <c r="Y69" t="s" s="2">
+        <v>518</v>
+      </c>
+      <c r="Z69" t="s" s="2">
+        <v>519</v>
+      </c>
+      <c r="AA69" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB69" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC69" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD69" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE69" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF69" t="s" s="2">
+        <v>515</v>
+      </c>
+      <c r="AG69" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH69" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI69" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ69" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK69" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL69" t="s" s="2">
+        <v>520</v>
+      </c>
+      <c r="AM69" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN69" t="s" s="2">
         <v>21</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AN60">
+  <autoFilter ref="A1:AN69">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -8629,7 +9859,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI59">
+  <conditionalFormatting sqref="A2:AI68">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-procedure.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-procedure.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-30T11:14:45+00:00</t>
+    <t>2026-09-30T12:38:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-procedure.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-procedure.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-30T12:38:12+00:00</t>
+    <t>2026-09-30T12:52:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-procedure.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-procedure.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-30T12:52:09+00:00</t>
+    <t>2026-09-30T14:46:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-procedure.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-procedure.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-30T14:46:14+00:00</t>
+    <t>2026-10-01T13:01:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1040,7 +1040,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://hl7.at/fhir/HL7ATCoreProfiles/4.0.1/StructureDefinition/at-core-patient)
+    <t xml:space="preserve">Reference(https://fhir.hl7.at/core/r4/StructureDefinition/at-core-patient)
 </t>
   </si>
   <si>
@@ -1121,7 +1121,7 @@
     <t>Procedure.recorder</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://hl7.at/fhir/HL7ATCoreProfiles/4.0.1/StructureDefinition/at-core-practitioner|http://hl7.at/fhir/HL7ATCoreProfiles/4.0.1/StructureDefinition/at-core-practitionerRole)
+    <t xml:space="preserve">Reference(https://fhir.hl7.at/core/r4/StructureDefinition/at-core-practitioner|https://fhir.hl7.at/core/r4/StructureDefinition/at-core-practitionerRole)
 </t>
   </si>
   <si>
@@ -1140,7 +1140,7 @@
     <t>Procedure.asserter</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://hl7.at/fhir/HL7ATCoreProfiles/4.0.1/StructureDefinition/at-core-practitioner|http://hl7.at/fhir/HL7ATCoreProfiles/4.0.1/StructureDefinition/at-core-practitionerRole|http://hl7.at/fhir/HL7ATCoreProfiles/4.0.1/StructureDefinition/at-core-patient|RelatedPerson)
+    <t xml:space="preserve">Reference(https://fhir.hl7.at/core/r4/StructureDefinition/at-core-practitioner|https://fhir.hl7.at/core/r4/StructureDefinition/at-core-practitionerRole|https://fhir.hl7.at/core/r4/StructureDefinition/at-core-patient|https://fhir.hl7.at/elga/ediag/r4/StructureDefinition/at-elga-ediag-relatedperson)
 </t>
   </si>
   <si>
@@ -1971,7 +1971,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="213.203125" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="226.09375" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-procedure.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-procedure.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-01T13:01:54+00:00</t>
+    <t>2026-10-02T12:58:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-procedure.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-procedure.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-02T12:58:24+00:00</t>
+    <t>2026-10-07T14:48:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-procedure.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-procedure.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-07T14:48:24+00:00</t>
+    <t>2026-10-08T12:55:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-procedure.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-procedure.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-08T12:55:57+00:00</t>
+    <t>2026-10-08T13:59:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-procedure.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-procedure.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-08T13:59:28+00:00</t>
+    <t>2026-10-08T14:12:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-procedure.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-procedure.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-08T14:12:43+00:00</t>
+    <t>2026-10-08T15:20:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-procedure.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-procedure.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-08T15:20:56+00:00</t>
+    <t>2026-10-09T06:09:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-procedure.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-procedure.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-09T06:09:27+00:00</t>
+    <t>2026-10-09T08:15:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-procedure.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-procedure.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-09T08:15:54+00:00</t>
+    <t>2026-10-09T08:42:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1385,7 +1385,7 @@
     <t>Procedure.report</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(DiagnosticReport|4.0.1|DocumentReference|4.0.1|Composition|4.0.1)
+    <t xml:space="preserve">Reference(https://profiles.ihe.net/ITI/MHD/StructureDefinition/IHE.MHD.Minimal.DocumentReference)
 </t>
   </si>
   <si>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-procedure.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-procedure.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-09T08:42:14+00:00</t>
+    <t>2026-10-09T09:07:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-procedure.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-procedure.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-09T09:07:37+00:00</t>
+    <t>2026-10-09T12:41:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-procedure.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-procedure.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-09T12:41:54+00:00</t>
+    <t>2026-10-12T13:54:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-procedure.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-procedure.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-12T13:54:53+00:00</t>
+    <t>2026-10-12T14:06:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-procedure.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-procedure.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-12T14:06:36+00:00</t>
+    <t>2026-10-12T14:31:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-procedure.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-procedure.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-12T14:31:02+00:00</t>
+    <t>2026-10-13T07:15:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-procedure.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-procedure.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-13T07:15:40+00:00</t>
+    <t>2026-10-14T06:31:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-procedure.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-procedure.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-14T06:31:33+00:00</t>
+    <t>2026-10-15T07:03:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-procedure.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-procedure.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T07:03:41+00:00</t>
+    <t>2026-10-16T09:08:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -3391,7 +3391,7 @@
         <v>79</v>
       </c>
       <c r="H13" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="I13" t="s" s="2">
         <v>21</v>
@@ -3486,7 +3486,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="14" hidden="true">
+    <row r="14">
       <c r="A14" t="s" s="2">
         <v>168</v>
       </c>
@@ -3507,7 +3507,7 @@
         <v>87</v>
       </c>
       <c r="H14" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="I14" t="s" s="2">
         <v>21</v>
@@ -3846,7 +3846,7 @@
         <v>78</v>
       </c>
       <c r="G17" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="H17" t="s" s="2">
         <v>21</v>
@@ -4062,7 +4062,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="19" hidden="true">
+    <row r="19">
       <c r="A19" t="s" s="2">
         <v>208</v>
       </c>
@@ -4081,7 +4081,7 @@
         <v>87</v>
       </c>
       <c r="H19" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="I19" t="s" s="2">
         <v>21</v>
@@ -4178,7 +4178,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="20" hidden="true">
+    <row r="20">
       <c r="A20" t="s" s="2">
         <v>219</v>
       </c>
@@ -4197,7 +4197,7 @@
         <v>87</v>
       </c>
       <c r="H20" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="I20" t="s" s="2">
         <v>21</v>
